--- a/AAII_Financials/Yearly/MTA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/MTA_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="92">
   <si>
     <t>MTA</t>
   </si>
@@ -952,10 +952,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>500</v>
-      </c>
-      <c r="E14" s="3">
-        <v>-100</v>
+        <v>700</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>4</v>
       </c>
       <c r="F14" s="3">
         <v>-1200</v>
@@ -1153,10 +1153,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>1400</v>
+        <v>1200</v>
       </c>
       <c r="E20" s="3">
-        <v>-900</v>
+        <v>-1000</v>
       </c>
       <c r="F20" s="3">
         <v>-500</v>
@@ -1195,10 +1195,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>800</v>
+        <v>1000</v>
       </c>
       <c r="E21" s="3">
-        <v>-1100</v>
+        <v>-900</v>
       </c>
       <c r="F21" s="3">
         <v>-2100</v>
@@ -1657,10 +1657,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-1400</v>
+        <v>-1200</v>
       </c>
       <c r="E32" s="3">
-        <v>900</v>
+        <v>1000</v>
       </c>
       <c r="F32" s="3">
         <v>500</v>
